--- a/Noyabrsk/Справка_ППН_Ноябрьск.xlsx
+++ b/Noyabrsk/Справка_ППН_Ноябрьск.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка ППН Ноябрьск" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J59"/>
+  <dimension ref="A2:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -549,7 +549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-1 с УПСВ_ХМАО</t>
+          <t>Комерция Холмогорское ЦПС НВО_ЯНАО</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -559,19 +559,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ЦНСт 38/198</t>
+          <t xml:space="preserve">НПВ 1250/60 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>НА-НВО-3 СО</t>
+          <t>НА-НВО-2 СО</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2318</v>
+        <v>27042</v>
       </c>
       <c r="J14" t="n">
-        <v>61000190597</v>
+        <v>61000202354</v>
       </c>
     </row>
     <row r="15">
@@ -585,7 +585,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-1 с УПСВ_ХМАО</t>
+          <t>Комерция Холмогорское ЦПС НВО_ЯНАО</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ЦНСт 38/198</t>
+          <t xml:space="preserve">НПВ 1250/60 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>НА-НВО-4 СО</t>
+          <t>НА-НВО-3 СО</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>320</v>
+        <v>26014</v>
       </c>
       <c r="J15" t="n">
-        <v>61000294472</v>
+        <v>61000202363</v>
       </c>
     </row>
     <row r="16">
@@ -621,7 +621,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-1 с УПСВ_ХМАО</t>
+          <t>Комерция Холмогорское ЦПС НВО_ЯНАО</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -631,21 +631,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1Д 630/125</t>
+          <t xml:space="preserve">НПВ 1250/60 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>НА-НВП-1 СО</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8Д6</t>
-        </is>
+          <t>НА-НВО-4 СО</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>26015</v>
       </c>
       <c r="J16" t="n">
-        <v>61000327720</v>
+        <v>61000202372</v>
       </c>
     </row>
     <row r="17">
@@ -659,7 +657,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-1 с УПСВ_ХМАО</t>
+          <t>Холмогорское ДНС-1 с УПСВ НВО_ХМАО</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -669,21 +667,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1Д 630/125</t>
+          <t>ЦНСт 38/198</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>НА-НВП-2 СО</t>
+          <t>НА-НВО-3 СО</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>662</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>61000387765</t>
-        </is>
+        <v>2318</v>
+      </c>
+      <c r="J17" t="n">
+        <v>61000190597</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +693,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-3 с УПСВ_ХМАО</t>
+          <t>Холмогорское ДНС-1 с УПСВ НВО_ХМАО</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -712,14 +708,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>НА-НВО-2 СО</t>
+          <t>НА-НВО-4 СО</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3850</v>
+        <v>320</v>
       </c>
       <c r="J18" t="n">
-        <v>61000294477</v>
+        <v>61000294472</v>
       </c>
     </row>
     <row r="19">
@@ -733,7 +729,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Карамовское ДНС с УПСВ НВО</t>
+          <t>Холмогорское ДНС-1 с УПСВ НВП_ХМАО</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -743,19 +739,21 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ЦНСт 60-198</t>
+          <t>1Д 630/125</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>НА-НВО-3 СО</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>367</v>
+          <t>НА-НВП-1 СО</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8Д6</t>
+        </is>
       </c>
       <c r="J19" t="n">
-        <v>61000188230</v>
+        <v>61000327720</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +767,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Карамовское ДНС с УПСВ НВО</t>
+          <t>Холмогорское ДНС-1 с УПСВ НВП_ХМАО</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -779,20 +777,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ЦНСт 60-198</t>
+          <t>1Д 630/125</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>НА-НВО-4 СО</t>
+          <t>НА-НВП-2 СО</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>526</v>
+        <v>662</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>61000171835</t>
+          <t>61000387765</t>
         </is>
       </c>
     </row>
@@ -807,7 +805,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-4 НВО_ХМАО</t>
+          <t>Холмогорское ДНС-3 с УПСВ НВО_ХМАО</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -817,7 +815,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ЦНСт 60/198</t>
+          <t>ЦНСт 38/198</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1600</v>
+        <v>491</v>
       </c>
       <c r="J21" t="n">
-        <v>61000188226</v>
+        <v>61000190333</v>
       </c>
     </row>
     <row r="22">
@@ -843,7 +841,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ НВО</t>
+          <t>Холмогорское ДНС-3 с УПСВ НВО_ХМАО</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -853,19 +851,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ЦНСт 300-300</t>
+          <t>ЦНСт 38/198</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НА-НВО-5 СО</t>
+          <t>НА-НВО-2 СО</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>139</v>
+        <v>3850</v>
       </c>
       <c r="J22" t="n">
-        <v>61000234587</v>
+        <v>61000294477</v>
       </c>
     </row>
     <row r="23">
@@ -879,7 +877,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ НВО</t>
+          <t>Холмогорское ДНС-3 с УПСВ НПВ_ХМАО</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -889,21 +887,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1Д 630/125</t>
+          <t>1Д630/90</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>НА-НПВ-1 СО</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>8Д3</t>
-        </is>
+          <t>НА-НПВ-2 СО</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1091</v>
       </c>
       <c r="J23" t="n">
-        <v>61000328833</v>
+        <v>61000188238</v>
       </c>
     </row>
     <row r="24">
@@ -917,7 +913,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ НПВ</t>
+          <t>Холмогорское ДНС-3 с УПСВ НПВ_ХМАО</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -927,21 +923,21 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1Д 630-125-пкп-УХЛ3.1</t>
+          <t>1Д630/90</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>НА-НПВ-3 СО</t>
+          <t>НА-НПВ-4 СО</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8Ю7</t>
+          <t>10Я19</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>61000420987</v>
+        <v>61000491131</v>
       </c>
     </row>
     <row r="25">
@@ -955,7 +951,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Средне-Итур. ДНС с УПСВ НПВ</t>
+          <t>Карамовское ДНС с УПСВ НВО</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -965,87 +961,280 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1Д 630/90</t>
+          <t>ЦНСт 105-245</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>НА-НВО-1 СО</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>84</v>
+      </c>
+      <c r="J25" t="n">
+        <v>61000294438</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Карамовское ДНС с УПСВ НВО</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ЦНСт 180-425</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>НА-НВО-2 СО</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>160123</v>
+      </c>
+      <c r="J26" t="n">
+        <v>61000294421</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Карамовское ДНС с УПСВ НВО</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ЦНСт 60-198</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>НА-НВО-3 СО</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>367</v>
+      </c>
+      <c r="J27" t="n">
+        <v>61000188230</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Карамовское ДНС с УПСВ НВО</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ЦНСт 60-198</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>НА-НВО-4 СО</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>526</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>61000171835</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Карамовское ДНС с УПСВ НПВ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ЦНСс 300-120</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>НА-НПВ-1 СО</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>140016</v>
+      </c>
+      <c r="J29" t="n">
+        <v>61000222140</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Карамовское ДНС с УПСВ НПВ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1Д 630/90 </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>НА-НПВ-2 СО</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>230</v>
+      </c>
+      <c r="J30" t="n">
+        <v>61000188243</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Карамовское ДНС с УПСВ НПВ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1Д 630/90 </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>НА-НПВ-3 СО</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>11ж32</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>61000311936</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>№ п/п</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ЦЕХ</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>Работы по текущему ремонту</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Дата выполнения работ</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Подпись, ФИО механика (мастера)</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>№ ЗАКАЗА САП ТОРО</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Оборудование</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Марка оборудования</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Рег. №</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Зав №</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3И29</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>61000189175</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НВО_ХМАО</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ЦНСт 60/198</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>НА-НВО-1 СО</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J32" t="n">
+        <v>61000188226</v>
+      </c>
+    </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1054,7 +1243,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-3 с УПСВ_ХМАО</t>
+          <t>Холмогорское ДНС-4 НВО_ХМАО</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1064,24 +1253,26 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ЦНСт 38/198</t>
+          <t>ЦНС 38/198</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>НА-НВО-1 ТР</t>
+          <t>НА-НВО-2 СО</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>491</v>
-      </c>
-      <c r="J33" t="n">
-        <v>61000190333</v>
+        <v>489</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>61000294475</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1090,7 +1281,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-3 с УПСВ_ХМАО</t>
+          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1100,24 +1291,26 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1Д630/90</t>
+          <t>1Д 630/125(подрес 500 колесо)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>НА-НПВ-2 ТР</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1091</v>
+          <t>НА-НПВ-1 СО</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>4и21</t>
+        </is>
       </c>
       <c r="J34" t="n">
-        <v>61000188238</v>
+        <v>61000294488</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1126,7 +1319,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Карамовское ДНС с УПСВ НВО</t>
+          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1136,24 +1329,28 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ЦНСт 105-245</t>
+          <t>1Д 630/90</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>НА-НВО-1 ТР</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>84</v>
-      </c>
-      <c r="J35" t="n">
-        <v>61000294438</v>
+          <t>НА-НПВ-2 СО</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>9ж35</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>61000188248</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1162,7 +1359,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-4 НВО_ХМАО</t>
+          <t>Пограничное УПСВГ НВО</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1172,26 +1369,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ЦНС 38/198</t>
+          <t>ЦНСт 300-360 (300)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>НА-НВО-2 ТР</t>
+          <t>НА-НВО-1 СО</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>489</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>61000294475</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="J36" t="n">
+        <v>61000294575</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1200,7 +1395,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
+          <t>Пограничное УПСВГ НВО</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1210,28 +1405,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1Д 630/125(подрез 500 колесо)</t>
+          <t>ЦНСс 300-360 (300)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>НА-НПВ-2 ТР</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>9У2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>61000294573</t>
-        </is>
+          <t>НА-НВО-2 СО</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>140</v>
+      </c>
+      <c r="J37" t="n">
+        <v>61000191186</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1250,24 +1441,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ЦНСт 300-360 (300)</t>
+          <t>ЦНСт 300-300</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>НА-НВО-1 ТР</t>
+          <t>НА-НВО-4 СО</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>93</v>
+        <v>150063</v>
       </c>
       <c r="J38" t="n">
-        <v>61000294575</v>
+        <v>61000191200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1286,26 +1477,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ЦНС 60-198</t>
+          <t>ЦНСт 300-300</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>НА-НВО-7 ТР</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>4м01</t>
-        </is>
+          <t>НА-НВО-5 СО</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>139</v>
       </c>
       <c r="J39" t="n">
-        <v>61000284440</v>
+        <v>61000234587</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1314,7 +1503,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Спорышевское ДНС-2 с УПСВ НВО</t>
+          <t>Пограничное УПСВГ НВО</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1324,28 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ЦНСт 105/294</t>
+          <t>ЦНСт 180-255</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>НА-НВО-3 ТР</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>94т</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>61000471297</t>
-        </is>
+          <t>НА-НВО-6 СО</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>24</v>
+      </c>
+      <c r="J40" t="n">
+        <v>61000191220</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1354,7 +1539,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
+          <t>Пограничное УПСВГ НВО</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1364,26 +1549,26 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1Д 1250-125 прав</t>
+          <t>ЦНС 60-198</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>НА-НПВ-4 ТР</t>
+          <t>НА-НВО-7 СО</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11Б4</t>
+          <t>4м01</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>61000536760</v>
+        <v>61000284440</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1392,7 +1577,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
+          <t>Пограничное УПСВГ НВО</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1402,26 +1587,26 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1Д 1250-125 (нерж.) прав</t>
+          <t>1Д 630/125</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>НА-НПВ-5 ТР</t>
+          <t>НА-НПВ-1 СО</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10Я8</t>
+          <t>8Д3</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>61000494812</v>
+        <v>61000328833</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1430,7 +1615,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Средне-Итур. ДНС с УПСВ НВО</t>
+          <t>Пограничное УПСВГ НПВ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1440,24 +1625,26 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ЦНСт 60/264</t>
+          <t>1Д 1250/125</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>НА-НВО-3 ТР</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>18</v>
+          <t>НА-НПВ-2 СО</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>С1400</t>
+        </is>
       </c>
       <c r="J43" t="n">
-        <v>61000171814</v>
+        <v>61000491133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1466,7 +1653,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Средне-Итур. ДНС с УПСВ НПВ</t>
+          <t>Пограничное УПСВГ НПВ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1476,87 +1663,254 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1Д630-90-Т-К-Е</t>
+          <t>1Д 630-125-пкп-УХЛ3.1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>НА-НПВ-1 ТР</t>
+          <t>НА-НПВ-3 СО</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10Я18</t>
+          <t>8Ю7</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>61000491132</v>
+        <v>61000420987</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>32</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Спорышевское ДНС-2 с УПСВ НВО</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ЦНС 60/198</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>НА-НВО-1 СО</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>57</v>
+      </c>
+      <c r="J45" t="n">
+        <v>61000540102</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>№ п/п</t>
-        </is>
+      <c r="A46" t="n">
+        <v>33</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ЦЕХ</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Работы по замене агрегатов</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Дата выполнения работ</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Подпись, ФИО механика (мастера)</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>№ ЗАКАЗА САП ТОРО</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Спорышевское ДНС-2 с УПСВ НВО</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ЦНСт 105/294</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>НА-НВО-2 СО</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>456</v>
+      </c>
+      <c r="J46" t="n">
+        <v>61000294433</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>34</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Спорышевское ДНС-2 с УПСВ НВО</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ЦНСт 105/294</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>НА-НВО-3 СО</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>94т</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>61000471297</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
+      <c r="A48" t="n">
+        <v>35</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Объект</t>
+          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Рег. №</t>
+          <t>насос</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Демонтаж</t>
+          <t>1Д 630-125</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Монтаж/ПНР</t>
+          <t>НА-НПВ-2 СО</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Марка оборудования</t>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
+          <t>9ф5</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>61000294491</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>36</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1Д 1250-125 прав</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>НА-НПВ-3 СО</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7М17</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>61000113893</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>37</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1Д 1250-125 прав</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>НА-НПВ-4 СО</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>12Б1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>61000537556</t>
+        </is>
+      </c>
+    </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1565,30 +1919,36 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
+          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>НА-НПВ-3</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>131</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1Д 1250-125 (нерж.) прав</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>НА-НПВ-5 СО</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ЦНС 300/120</t>
+          <t>10Я8</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>61000190357</v>
+        <v>61000494812</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1597,34 +1957,36 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
+          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>НА-НПВ-3</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1Д 1250-125</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2-369</t>
+          <t>НА-НПВ-6 СО</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ЦНС 300/120</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>61000311895</t>
-        </is>
+          <t>12Б2</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>61000537115</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1633,34 +1995,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ НВО</t>
+          <t>Средне-Итур. ДНС с УПСВ НВО</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>НА-НВО-3</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ЦНСт 38/198</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2-97</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>ЦНСт 300-360 (300)</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>61000191179</t>
-        </is>
+          <t>НА-НВО-1 СО</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>650</v>
+      </c>
+      <c r="J53" t="n">
+        <v>61000294476</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1669,32 +2031,34 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ НВ</t>
+          <t>Средне-Итур. ДНС с УПСВ НВО</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>НА-НВ-1</t>
+          <t>насос</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>9Ж23</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>1Д 200/90</t>
-        </is>
+          <t>ЦНСт 60/264</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>НА-НВО-3 СО</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>61000191343</v>
+        <v>61000171814</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1703,34 +2067,36 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ НВ</t>
+          <t>Средне-Итур. ДНС с УПСВ НПВ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>НА-НВ-1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1Д630-90-Т-К-Е</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2-1222</t>
+          <t>НА-НПВ-1 СО</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1Д 200-90-т-Е УХЛ 3.1 (новый)</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>61000532802</t>
-        </is>
+          <t>10Я18</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>61000491132</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1739,32 +2105,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ ПН</t>
+          <t>Средне-Итур. ДНС с УПСВ НПВ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>НА-ПН-1</t>
+          <t>насос</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3А23</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>1Д 630/125</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>НА-НПВ-2 СО</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1Д 200/90</t>
+          <t>10Т9</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>61000191379</v>
+        <v>61000294487</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1773,135 +2143,1155 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Пограничное УПСВГ ПН</t>
+          <t>Средне-Итур. ДНС с УПСВ НПВ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>НА-ПН-1</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1Д 630/90</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2-1223</t>
+          <t>НА-НПВ-3 СО</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1Д 200-90-т-Е УХЛ 3.1 (новый)</t>
+          <t>11ж32</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>61000532803</v>
+        <v>61000311936</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
+        <v>45</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Средне-Итур. ДНС с УПСВ НППВ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ЦНСт 60/198</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>НА-НППВ-2 СО</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>80</v>
+      </c>
+      <c r="J58" t="n">
+        <v>61000294457</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Работы по текущему ремонту</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Зав №</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Работы по замене агрегатов</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Монтаж/ПНР</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Комерция Холмогорское ЦПС НВО_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>НА-НВО-1</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>47286</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">НПВ 1250/60 </t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>61000311071</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Комерция Холмогорское ЦПС НВО_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>НА-НВО-1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>47286</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">НПВ 1250/60 </t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>61000311071</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Холмогорское ЦПС НП_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>НА-НП-13</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>446</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>12НА 9/4</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>61000312043</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Холмогорское ЦПС НП_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>НА-НП-13</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>12НА 9/4</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>61000494992</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НП_ХМАО</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>НА-ЕП ДНС</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>2509</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>НВ 50/50</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>61000294514</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>6</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>НА-НД-1</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>749</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>61000189099</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>НА-НД-2</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>712441</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>61000537106</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>8</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>ЦППН-1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>НА-НД-2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>712441</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>61000537106</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>НА-НД-3</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>99030</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>61000189108</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>10</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>НА-НД-3</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>99030</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>61000189108</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>НА-НД-4</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>5Т76</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>НШ 5/25</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>61000189105</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>12</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-3 с УПСВ НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>НА-НД-4</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>5Т76</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>НШ 5/25</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>61000189105</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>13</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НВО_ХМАО</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>НА-НВО-3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>459</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ЦНСт 105/490</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>61000311952</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>14</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>НА-НПВ-3</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>131</v>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ЦНС 300/120</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>61000190357</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>15</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НПВ_ХМАО</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>НА-НПВ-3</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>123</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ЦНС 300/120</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>61000311895</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>16</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>НА-НД-1</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>99025</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>61000190399</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>17</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>НА-НД-1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>712442</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>НД 2,5/400</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>61000537104</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>18</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>НА-НД-2</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>96011</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ДП 4/250</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>61000190400</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>19</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>НА-НД-2</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>712478</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>НД 1,0 10/100 К13В УХЛ3</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>61000537111</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>20</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>НА-НД-3</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>5П111</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>НШ 5/25</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>61000294555</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>21</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Холмогорское ДНС-4 НД_ХМАО</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>НА-НД-3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>5П111</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>НШ 5/25</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>61000294555</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>22</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Пограничное УПСВГ НВО</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>НА-НВО-3</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>252</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ЦНСс 300-360 (300)</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>61000191193</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>23</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Пограничное УПСВГ НВО</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>НА-НВО-3</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>924</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ЦНСт 300-360 (300)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>61000191179</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>24</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Пограничное УПСВГ НВ</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>НА-НВ-1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>9Ж23</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1Д 200/90</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>61000191343</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>25</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Пограничное УПСВГ НВ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>НА-НВ-1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>8б34</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1Д 200-90-т-Е УХЛ 3.1 (новый)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>61000532802</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>26</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Пограничное УПСВГ ПН</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>НА-ПН-1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3А23</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1Д 200/90</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>61000191379</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>27</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Пограничное УПСВГ ПН</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>НА-ПН-1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>8б36</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1Д 200-90-т-Е УХЛ 3.1 (новый)</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>61000532803</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>28</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ЦППН-1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
         <is>
           <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>НА-НПВ-1</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>590</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>1Д 630-125</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>61000190616</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>ЦППН-1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Спорышевское ДНС-2 с УПСВ НПВ</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>НА-НПВ-6</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>12Б2</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1Д 1250-125</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>61000537115</v>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>11Б3</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1Д1250-125</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>61000536759</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="C46:G47"/>
-    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="I61:I64"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E69:E70"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C67:G68"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="C61:G62"/>
     <mergeCell ref="H9:H12"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="H5"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="I28:I31"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B61:B64"/>
     <mergeCell ref="F4"/>
-    <mergeCell ref="J28:J31"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="H61:H64"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G63:G64"/>
     <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C28:G29"/>
     <mergeCell ref="F3"/>
-    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="I67:I70"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="D63:D64"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="F2"/>
+    <mergeCell ref="F63:F64"/>
     <mergeCell ref="I9:I12"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="J46:J49"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="F69:F70"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I46:I49"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="J67:J70"/>
     <mergeCell ref="C9:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
